--- a/doc/Design_Doc/gantt.xlsx
+++ b/doc/Design_Doc/gantt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://penno365-my.sharepoint.com/personal/tonytg_upenn_edu/Documents/Penn/CIS 6600/Authoring Tool/ButterFlight/doc/Design_Doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E919E09-1F5B-4360-9B93-F97FCBA7CEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{69663E83-51A1-E54E-B0CD-F88F5C3E4BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5977683B-3626-D149-8D4D-23FBD49AEE42}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{49EA0230-CB7E-48F8-94F3-411FE65DEB95}"/>
+    <workbookView xWindow="20" yWindow="680" windowWidth="34180" windowHeight="19800" xr2:uid="{00BC18C4-74FF-AF4B-8E1E-B50CC671D202}"/>
   </bookViews>
   <sheets>
     <sheet name="gantt" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="77">
   <si>
     <t>ID</t>
   </si>
@@ -28,79 +28,184 @@
     <t>Task Name</t>
   </si>
   <si>
-    <t>Week 1</t>
-  </si>
-  <si>
-    <t>Week 2</t>
-  </si>
-  <si>
-    <t>Week 3</t>
-  </si>
-  <si>
-    <t>Week 4</t>
-  </si>
-  <si>
-    <t>Week 5</t>
-  </si>
-  <si>
-    <t>Week 6</t>
-  </si>
-  <si>
-    <t>Week 7</t>
-  </si>
-  <si>
-    <t>Week 8</t>
-  </si>
-  <si>
-    <t>Week 9</t>
-  </si>
-  <si>
-    <t>Week 10</t>
-  </si>
-  <si>
-    <t>Week 11</t>
-  </si>
-  <si>
-    <t>Dates</t>
-  </si>
-  <si>
-    <t>Design Doc</t>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Assigned</t>
+  </si>
+  <si>
+    <t>W1 (Feb 25)</t>
+  </si>
+  <si>
+    <t>W2 (Mar 4)</t>
+  </si>
+  <si>
+    <t>W3 (Mar 11)</t>
+  </si>
+  <si>
+    <t>W4 (Mar 18)</t>
+  </si>
+  <si>
+    <t>W5 (Mar 25)</t>
+  </si>
+  <si>
+    <t>W6 (Apr 1)</t>
+  </si>
+  <si>
+    <t>W7 (Apr 8)</t>
+  </si>
+  <si>
+    <t>W8 (Apr 15)</t>
+  </si>
+  <si>
+    <t>W9 (Apr 22)</t>
+  </si>
+  <si>
+    <t>W10 (Apr 29)</t>
+  </si>
+  <si>
+    <t>W11 (May 6)</t>
+  </si>
+  <si>
+    <t>Spring Break (Mar 6-15) --- No Work</t>
+  </si>
+  <si>
+    <t>Env Setup &amp; Scaffolding</t>
+  </si>
+  <si>
+    <t>1 week</t>
   </si>
   <si>
     <t>C&amp;Y</t>
   </si>
   <si>
-    <t>Env Setup &amp; Scaffolding</t>
+    <t>CMake Build Configuration</t>
+  </si>
+  <si>
+    <t>2 days</t>
+  </si>
+  <si>
+    <t>BFSimulateCmd Skeleton</t>
+  </si>
+  <si>
+    <t>MEL Round-Trip Verification</t>
+  </si>
+  <si>
+    <t>1 day</t>
   </si>
   <si>
     <t>Skeleton Rig &amp; Maneuvering Fns</t>
   </si>
   <si>
+    <t>2 weeks</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
+    <t>Y*</t>
+  </si>
+  <si>
+    <t>BFState Struct &amp; Joint Enum</t>
+  </si>
+  <si>
+    <t>Maneuvering Function (Eqs. 1-3)</t>
+  </si>
+  <si>
+    <t>3 days</t>
+  </si>
+  <si>
+    <t>Joint-Rotation Applicator</t>
+  </si>
+  <si>
+    <t>Visual Verification</t>
+  </si>
+  <si>
     <t>Aerodynamic Force Model</t>
   </si>
   <si>
+    <t>1.5 weeks</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
+    <t>C*</t>
+  </si>
+  <si>
+    <t>Wing-Panel Normal Computation</t>
+  </si>
+  <si>
+    <t>Lift/Drag Polynomial Eval (Eqs. 4-6)</t>
+  </si>
+  <si>
+    <t>Newton Integration</t>
+  </si>
+  <si>
     <t>Curl-Noise Vortex Force</t>
   </si>
   <si>
+    <t>3-D Gradient Perlin Noise</t>
+  </si>
+  <si>
+    <t>Finite-Difference Curl (Eq. 7)</t>
+  </si>
+  <si>
+    <t>UI Integration</t>
+  </si>
+  <si>
     <t>Maneuver Control &amp; Decoupling</t>
   </si>
   <si>
+    <t>Preferred Acceleration (Eq. 8)</t>
+  </si>
+  <si>
+    <t>Local Accel Decoupling (Eqs. 10-11)</t>
+  </si>
+  <si>
+    <t>Sliding-Window Smoother (Eq. 12)</t>
+  </si>
+  <si>
     <t>MEL/Python UI Panel</t>
   </si>
   <si>
+    <t>Full Control Layout</t>
+  </si>
+  <si>
+    <t>Callbacks</t>
+  </si>
+  <si>
+    <t>Command Invocation &amp; Bake</t>
+  </si>
+  <si>
     <t>Alpha Demo Integration</t>
   </si>
   <si>
+    <t>0.5 weeks</t>
+  </si>
+  <si>
     <t>*1</t>
   </si>
   <si>
-    <t>Swarm Simulation</t>
+    <t>End-to-End Integration Test</t>
+  </si>
+  <si>
+    <t>Integration Bug Fixes</t>
+  </si>
+  <si>
+    <t>Alpha Scene Packaging</t>
+  </si>
+  <si>
+    <t>Swarm Simulation &amp; Aggregation</t>
+  </si>
+  <si>
+    <t>Multi-Agent State Management</t>
+  </si>
+  <si>
+    <t>Centroid-Based Preferred Accel</t>
+  </si>
+  <si>
+    <t>Swarm UI &amp; Demo Scene</t>
   </si>
   <si>
     <t>Export &amp; Beta Integration</t>
@@ -109,13 +214,31 @@
     <t>*2</t>
   </si>
   <si>
+    <t>Export Cache Button</t>
+  </si>
+  <si>
+    <t>Wind Parameter Round-Trip</t>
+  </si>
+  <si>
+    <t>Beta Scene Packaging &amp; Tag</t>
+  </si>
+  <si>
     <t>Testing &amp; Final Demo</t>
   </si>
   <si>
     <t>*3</t>
   </si>
   <si>
-    <t>*1 = Alpha version release (Mar 25)</t>
+    <t>Regression Testing</t>
+  </si>
+  <si>
+    <t>Swarm Performance Profiling</t>
+  </si>
+  <si>
+    <t>Quick-Start PDF &amp; Code Submission</t>
+  </si>
+  <si>
+    <t>*1 = Alpha version release (~Apr 8)</t>
   </si>
   <si>
     <t>*2 = Beta version release (Apr 15)</t>
@@ -124,72 +247,26 @@
     <t>*3 = Final Demo (May 5) / Code Due (May 11)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="7" tint="-0.249977111117893"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C = Cecilia Chen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> | </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="6" tint="0.39997558519241921"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y = Yiding Tian</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> | </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C&amp;Y = Both</t>
-    </r>
+    <t>C = Cecilia Chen | Y = Yiding Tian | C&amp;Y = Both</t>
+  </si>
+  <si>
+    <t>* = Partial week --- both unavailable from Mar 6 (Spring Break)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -227,28 +304,28 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF9C5700"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF3F3F76"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -256,7 +333,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -264,14 +341,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -279,14 +356,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -294,7 +371,7 @@
     </font>
     <font>
       <i/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF7F7F7F"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -302,42 +379,28 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="7" tint="-0.249977111117893"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="5" tint="-0.249977111117893"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="6" tint="0.39997558519241921"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -515,42 +578,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -714,32 +741,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -785,7 +792,50 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1114,272 +1164,851 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9854EFDC-6051-4A0C-86F7-753064FA408D}">
-  <dimension ref="A1:M18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DA11BDF-014B-1C46-8614-977D8EBD12AA}">
+  <dimension ref="A1:O49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="39.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.26953125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.453125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.7265625" style="1"/>
+    <col min="2" max="2" width="52.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="13" max="13" width="11.5" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B2" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2">
-        <v>46078</v>
-      </c>
-      <c r="D2" s="2">
-        <v>46085</v>
-      </c>
-      <c r="E2" s="2">
-        <v>46092</v>
-      </c>
-      <c r="F2" s="2">
-        <v>46099</v>
-      </c>
-      <c r="G2" s="2">
-        <v>46106</v>
-      </c>
-      <c r="H2" s="2">
-        <v>46113</v>
-      </c>
-      <c r="I2" s="2">
-        <v>46120</v>
-      </c>
-      <c r="J2" s="2">
-        <v>46127</v>
-      </c>
-      <c r="K2" s="2">
-        <v>46134</v>
-      </c>
-      <c r="L2" s="2">
-        <v>46141</v>
-      </c>
-      <c r="M2" s="2">
-        <v>46148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="2" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1.2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1.3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2.1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>2.4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>3</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>3.1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>3.2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>3.3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>4.2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="D18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>4.3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>5.2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>5.3</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>6.1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>6.2</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="D26" t="s">
+        <v>35</v>
+      </c>
+      <c r="J26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>6.3</v>
+      </c>
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
+      <c r="B28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" t="s">
+        <v>18</v>
+      </c>
+      <c r="K28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>7.1</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>7.2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>7.3</v>
+      </c>
+      <c r="B31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
+      <c r="B32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>8.1</v>
+      </c>
+      <c r="B33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="B35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
         <v>9</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="B36" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" t="s">
+        <v>35</v>
+      </c>
+      <c r="K36" t="s">
+        <v>35</v>
+      </c>
+      <c r="L36" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>9.1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>35</v>
+      </c>
+      <c r="K37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="B38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="B39" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" t="s">
+        <v>35</v>
+      </c>
+      <c r="K39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>10</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="L40" t="s">
+        <v>18</v>
+      </c>
+      <c r="M40" t="s">
+        <v>18</v>
+      </c>
+      <c r="N40" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>10.1</v>
+      </c>
+      <c r="B41" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="L41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="B42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>10</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B15" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B16" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B17" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B18" s="1" t="s">
-        <v>34</v>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="M42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>10.3</v>
+      </c>
+      <c r="B43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="N43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <conditionalFormatting sqref="A3:B43">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:N43">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Y">
+      <formula>NOT(ISERROR(SEARCH("Y",D3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="C">
+      <formula>NOT(ISERROR(SEARCH("C",D3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="C&amp;Y">
+      <formula>NOT(ISERROR(SEARCH("C&amp;Y",D3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>